--- a/artfynd/A 31213-2026 artfynd.xlsx
+++ b/artfynd/A 31213-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269747</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269748</v>
       </c>
       <c r="B3" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137269749</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>137269750</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137269751</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2026 artfynd.xlsx
+++ b/artfynd/A 31213-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269747</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269748</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137269749</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>137269750</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137269751</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2026 artfynd.xlsx
+++ b/artfynd/A 31213-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269747</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269748</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137269749</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>137269750</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137269751</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2026 artfynd.xlsx
+++ b/artfynd/A 31213-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269747</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2026 artfynd.xlsx
+++ b/artfynd/A 31213-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269747</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2026 artfynd.xlsx
+++ b/artfynd/A 31213-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269747</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2026 artfynd.xlsx
+++ b/artfynd/A 31213-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137269747</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137269748</v>
       </c>
       <c r="B3" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137269749</v>
       </c>
       <c r="B4" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>137269750</v>
       </c>
       <c r="B5" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137269751</v>
       </c>
       <c r="B6" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
